--- a/data/ct_scoop/ct_scoop_links_2026-05-12.xlsx
+++ b/data/ct_scoop/ct_scoop_links_2026-05-12.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,112 +440,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STORRS SCOOP: Monmouth Trading Cards coming soon to Storrs Center</t>
+          <t>SOUTH WINDSOR SCOOP: New pottery studio opening later this month!</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/storrs-scoop-monmouth-trading-cards-coming-soon-to-storrs-center</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/south-windsor-scoop-new-pottery-studio-opening-later-this-month</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WATERBURY SCOOP: Soft Serve Factory replaces Carvel in Waterbury!</t>
+          <t>NEWINGTON SCOOP: Large-scale development eyed in Newington</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/waterbury-scoop-soft-serve-factory-replaces-carvel-in-waterbury</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/newington-scoop-large-scale-development-eyed-in-newington</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FOXWOODS SCOOP: Hell's Kitchen back for 2 more seasons!</t>
+          <t>DANBURY SCOOP: Paris Baguette coming soon to Danbury Fair</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/foxwoods-scoop-hells-kitchen-back-for-2-more-seasons</t>
+          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/danbury-scoop-paris-baguette-coming-soon-to-danbury-fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PUTNAM SCOOP: New Candle Shop coming soon to Putnam</t>
+          <t>CROMWELL SCOOP: Wingstop coming to Cromwell</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46152</v>
+        <v>46154</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-windham-county-posts/putnam-scoop-new-candle-shop-coming-soon-to-putnam</t>
+          <t>https://www.theconnecticutscoop.com/all-middlesex-county-posts/cromwell-scoop-wingstop-coming-to-cromwell</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MANCHESTER SCOOP: Nothing Bundt Cakes planning Manchester location!</t>
+          <t>STORRS SCOOP: Monmouth Trading Cards coming soon to Storrs Center</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-nothing-bundt-cakes-planning-manchester-location</t>
+          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/storrs-scoop-monmouth-trading-cards-coming-soon-to-storrs-center</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WEST HARTFORD SCOOP: Frisbie's Dairy Barn officially opens in WeHa!</t>
+          <t>WATERBURY SCOOP: Soft Serve Factory replaces Carvel in Waterbury!</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-frisbies-dairy-barn-officially-opens-in-weha</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/waterbury-scoop-soft-serve-factory-replaces-carvel-in-waterbury</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CANTON SCOOP: The Frosted Sheep Bake Shop opens in Canton</t>
+          <t>FOXWOODS SCOOP: Hell's Kitchen back for 2 more seasons!</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/canton-scoop-the-frosted-sheep-bake-shop-opens-in-canton</t>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/foxwoods-scoop-hells-kitchen-back-for-2-more-seasons</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRANFORD SCOOP: O'Reilly Auto Parts eyeing Branford location</t>
+          <t>PUTNAM SCOOP: New Candle Shop coming soon to Putnam</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -553,14 +553,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/branford-scoop-oreilly-auto-parts-eyeing-branford-location</t>
+          <t>https://www.theconnecticutscoop.com/all-windham-county-posts/putnam-scoop-new-candle-shop-coming-soon-to-putnam</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MERIDEN SCOOP: Don Cola'o Panaderia opens in Meriden</t>
+          <t>MANCHESTER SCOOP: Nothing Bundt Cakes planning Manchester location!</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -568,14 +568,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/meriden-scoop-don-colao-panaderia-opens-in-meriden</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-nothing-bundt-cakes-planning-manchester-location</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EAST LYME SCOOP: Mystic Market sets opening date!</t>
+          <t>WEST HARTFORD SCOOP: Frisbie's Dairy Barn officially opens in WeHa!</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -583,14 +583,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/east-lyme-scoop-mystic-market-sets-opening-date</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-frisbies-dairy-barn-officially-opens-in-weha</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FOXWOODS SCOOP: New tenants are popping up at Tanger Outlets</t>
+          <t>CANTON SCOOP: The Frosted Sheep Bake Shop opens in Canton</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -598,20 +598,80 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/foxwoods-scoop-new-tenants-are-popping-up-at-tanger-outlets</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/canton-scoop-the-frosted-sheep-bake-shop-opens-in-canton</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>BRANFORD SCOOP: O'Reilly Auto Parts eyeing Branford location</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/branford-scoop-oreilly-auto-parts-eyeing-branford-location</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MERIDEN SCOOP: Don Cola'o Panaderia opens in Meriden</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/meriden-scoop-don-colao-panaderia-opens-in-meriden</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EAST LYME SCOOP: Mystic Market sets opening date!</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/east-lyme-scoop-mystic-market-sets-opening-date</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FOXWOODS SCOOP: New tenants are popping up at Tanger Outlets</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/foxwoods-scoop-new-tenants-are-popping-up-at-tanger-outlets</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>MOHEGAN SUN SCOOP: Take a look at the new Bobby's Burgers!</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>46152</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B17" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/mohegan-sun-scoop-take-a-look-at-the-new-bobbys-burgers</t>
         </is>
